--- a/sources/kunimitsu_step6b.xlsx
+++ b/sources/kunimitsu_step6b.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -794,17 +794,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1+3 [tag]</t>
+          <t>1+3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2+4 [tag]; 2+5 [tag]</t>
+          <t>2+4; 2+5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tornado [Tag]</t>
+          <t>Tornado</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -830,6 +830,11 @@
       <c r="O8" t="inlineStr">
         <is>
           <t>Only does 20 damage if you tag.</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">

--- a/sources/kunimitsu_step6b.xlsx
+++ b/sources/kunimitsu_step6b.xlsx
@@ -780,6 +780,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>30789c48-adc1-43a6-8721-635dee152db2</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>30789c48-adc1-43a6-8721-635dee152db2</t>
@@ -837,6 +842,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>49442819-bc2b-4f48-91c4-56203c67f51a</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>49442819-bc2b-4f48-91c4-56203c67f51a</t>
@@ -882,6 +892,11 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>66c176e2-e46f-45a2-84bf-6b63c3ac4a23</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -4758,6 +4773,11 @@
       <c r="K84" t="inlineStr">
         <is>
           <t>hmm"h"h"Lmhm"!</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>de1828d4-6182-4a4b-8d22-85b48de701af</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
